--- a/artfynd/A 50386-2022 artfynd.xlsx
+++ b/artfynd/A 50386-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50386-2022 artfynd.xlsx
+++ b/artfynd/A 50386-2022 artfynd.xlsx
@@ -1716,12 +1716,7 @@
         <v>104535298</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,16 +1742,25 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603444.4764166221</v>
+        <v>603445</v>
       </c>
       <c r="R11" t="n">
-        <v>6461022.971627477</v>
+        <v>6461023</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1786,27 +1790,18 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50386-2022 artfynd.xlsx
+++ b/artfynd/A 50386-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>232083</v>
       </c>
       <c r="B2" t="n">
-        <v>73679</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603575.8944152282</v>
+        <v>603576</v>
       </c>
       <c r="R2" t="n">
-        <v>6460976.433146967</v>
+        <v>6460976</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +743,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,12 +785,7 @@
         <v>448080</v>
       </c>
       <c r="B3" t="n">
-        <v>73614</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603461.1054829784</v>
+        <v>603461</v>
       </c>
       <c r="R3" t="n">
-        <v>6460991.839075445</v>
+        <v>6460992</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,19 +850,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2000-01-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,15 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104517505</v>
+        <v>104535270</v>
       </c>
       <c r="B4" t="n">
-        <v>4717</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -930,38 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>2590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603563.8316174119</v>
+        <v>603474</v>
       </c>
       <c r="R4" t="n">
-        <v>6461155.000821551</v>
+        <v>6461048</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,19 +952,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,27 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104518247</v>
+        <v>104535243</v>
       </c>
       <c r="B5" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,38 +992,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603548.4724679148</v>
+        <v>603598</v>
       </c>
       <c r="R5" t="n">
-        <v>6460956.772901183</v>
+        <v>6460950</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,19 +1049,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,27 +1066,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104518653</v>
+        <v>104535244</v>
       </c>
       <c r="B6" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,38 +1089,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603420.0459559158</v>
+        <v>603546</v>
       </c>
       <c r="R6" t="n">
-        <v>6460989.711310497</v>
+        <v>6460983</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,19 +1146,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,66 +1163,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104517511</v>
+        <v>104535245</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603560.0617401284</v>
+        <v>603531</v>
       </c>
       <c r="R7" t="n">
-        <v>6461158.058658758</v>
+        <v>6460974</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,19 +1243,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,27 +1260,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Eva Siljeholm, Olle Jonsson, Torbjörn Blixt</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104517603</v>
+        <v>104535246</v>
       </c>
       <c r="B8" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,38 +1283,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>2818</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603567.5021835074</v>
+        <v>603446</v>
       </c>
       <c r="R8" t="n">
-        <v>6461035.14044563</v>
+        <v>6461033</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,19 +1340,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,70 +1357,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104517599</v>
+        <v>104535247</v>
       </c>
       <c r="B9" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderköping, Ög</t>
+          <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603580.2599601175</v>
+        <v>603478</v>
       </c>
       <c r="R9" t="n">
-        <v>6461071.251976661</v>
+        <v>6461052</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,24 +1437,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2tallar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,65 +1454,61 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Jonsson</t>
+          <t>Marika Sjödin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104535246</v>
+        <v>104517511</v>
       </c>
       <c r="B10" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2818</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603445.268243446</v>
+        <v>603560</v>
       </c>
       <c r="R10" t="n">
-        <v>6461032.988905767</v>
+        <v>6461158</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1674,19 +1535,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,69 +1552,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm, Olle Jonsson, Torbjörn Blixt</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104535298</v>
+        <v>104517599</v>
       </c>
       <c r="B11" t="n">
-        <v>5177</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603445</v>
+        <v>603580</v>
       </c>
       <c r="R11" t="n">
-        <v>6461023</v>
+        <v>6461071</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,78 +1642,78 @@
           <t>2022-11-07</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2tallar</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Olle Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104535270</v>
+        <v>104517603</v>
       </c>
       <c r="B12" t="n">
-        <v>94160</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2590</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603474.394371176</v>
+        <v>603567</v>
       </c>
       <c r="R12" t="n">
-        <v>6461047.957536224</v>
+        <v>6461036</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1893,19 +1740,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,65 +1757,61 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104535243</v>
+        <v>104518653</v>
       </c>
       <c r="B13" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2818</v>
+        <v>6426</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603598.7079531567</v>
+        <v>603420</v>
       </c>
       <c r="R13" t="n">
-        <v>6460950.724391777</v>
+        <v>6460990</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2005,19 +1838,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,65 +1855,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104535245</v>
+        <v>104519061</v>
       </c>
       <c r="B14" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2818</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603531.1612128301</v>
+        <v>603661</v>
       </c>
       <c r="R14" t="n">
-        <v>6460973.681735777</v>
+        <v>6460880</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2117,19 +1936,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,27 +1953,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104535244</v>
+        <v>104518247</v>
       </c>
       <c r="B15" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,37 +1976,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ängelholm, Ög</t>
+          <t>Söderköping, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603546.2028828773</v>
+        <v>603548</v>
       </c>
       <c r="R15" t="n">
-        <v>6460983.020494527</v>
+        <v>6460957</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2229,19 +2034,9 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-07</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,27 +2051,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marika Sjödin</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104535247</v>
+        <v>104535298</v>
       </c>
       <c r="B16" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,34 +2074,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2818</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Ängelholm, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603478.4981527429</v>
+        <v>603445</v>
       </c>
       <c r="R16" t="n">
-        <v>6461052.274114317</v>
+        <v>6461023</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2341,27 +2140,18 @@
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-07</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2377,6 +2167,299 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104517505</v>
+      </c>
+      <c r="B17" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Söderköping, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>603564</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6461156</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>104535286</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ängelholm, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>603587</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6460881</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marika Sjödin, Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>104519005</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Söderköping, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>603620</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6460874</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Söderköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sankt Anna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-11-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm, Torbjörn Blixt</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50386-2022 artfynd.xlsx
+++ b/artfynd/A 50386-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/232083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
           <t>Sällsynta lavar i Östergötland 2000</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/448080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535270</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535243</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535244</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535245</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1366,6 +1401,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535246</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1463,6 +1503,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535247</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1561,6 +1606,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104517511</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1668,6 +1718,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104517599</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1766,6 +1821,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104517603</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518653</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1962,6 +2027,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104519061</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2060,6 +2130,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104518247</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535298</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2265,6 +2345,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104517505</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2362,6 +2447,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104535286</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2460,8 +2550,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104519005</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>